--- a/network_excel_transformer/output/2G3G4G_Cell Info_SITES_4G.xlsx
+++ b/network_excel_transformer/output/2G3G4G_Cell Info_SITES_4G.xlsx
@@ -477,8 +477,10 @@
           <t>4G_GagnoaAnader</t>
         </is>
       </c>
-      <c r="C2" s="2" t="n">
-        <v>0</v>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>CI05066</t>
+        </is>
       </c>
       <c r="D2" s="2" t="n">
         <v>6.12014</v>
@@ -498,8 +500,10 @@
           <t>4G_BINHOUNIENSOUSPREFECTURE</t>
         </is>
       </c>
-      <c r="C3" s="2" t="n">
-        <v>1</v>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>CI05073</t>
+        </is>
       </c>
       <c r="D3" s="2" t="n">
         <v>6.78463</v>
@@ -519,8 +523,10 @@
           <t>4G_ROXGOLDNEW</t>
         </is>
       </c>
-      <c r="C4" s="2" t="n">
-        <v>2</v>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>CI05190</t>
+        </is>
       </c>
       <c r="D4" s="2" t="n">
         <v>8.097491</v>
@@ -540,8 +546,10 @@
           <t>4G_TOULEUPLEUMAIRIE</t>
         </is>
       </c>
-      <c r="C5" s="2" t="n">
-        <v>3</v>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>CI05074</t>
+        </is>
       </c>
       <c r="D5" s="2" t="n">
         <v>6.5773</v>
@@ -561,8 +569,10 @@
           <t>4G_ZAGNEGLAZA</t>
         </is>
       </c>
-      <c r="C6" s="2" t="n">
-        <v>4</v>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>CI05075</t>
+        </is>
       </c>
       <c r="D6" s="2" t="n">
         <v>6.21509</v>
@@ -582,8 +592,10 @@
           <t>4G_AdjameMotagri</t>
         </is>
       </c>
-      <c r="C7" s="2" t="n">
-        <v>5</v>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>CI05042</t>
+        </is>
       </c>
       <c r="D7" s="2" t="n">
         <v>5.37617</v>
@@ -603,8 +615,10 @@
           <t>4G_AdjameCampGalieni</t>
         </is>
       </c>
-      <c r="C8" s="2" t="n">
-        <v>6</v>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>CI04964</t>
+        </is>
       </c>
       <c r="D8" s="2" t="n">
         <v>5.33833</v>
@@ -624,8 +638,10 @@
           <t>4G_AboboVesos</t>
         </is>
       </c>
-      <c r="C9" s="2" t="n">
-        <v>7</v>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>CI05036</t>
+        </is>
       </c>
       <c r="D9" s="2" t="n">
         <v>5.43174</v>
@@ -645,8 +661,10 @@
           <t>4G_AssiniePoton</t>
         </is>
       </c>
-      <c r="C10" s="2" t="n">
-        <v>8</v>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>CI05021</t>
+        </is>
       </c>
       <c r="D10" s="2" t="n">
         <v>5.143529</v>
@@ -666,8 +684,10 @@
           <t>4G_AttecoubePoleBoulevardDeLaPaix</t>
         </is>
       </c>
-      <c r="C11" s="2" t="n">
-        <v>9</v>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>CI04983</t>
+        </is>
       </c>
       <c r="D11" s="2" t="n">
         <v>5.353634</v>
@@ -687,8 +707,10 @@
           <t>4G_BonouaDingui</t>
         </is>
       </c>
-      <c r="C12" s="2" t="n">
-        <v>10</v>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>CI05020</t>
+        </is>
       </c>
       <c r="D12" s="2" t="n">
         <v>5.28436</v>
@@ -708,8 +730,10 @@
           <t>4G_CocodyManhattan</t>
         </is>
       </c>
-      <c r="C13" s="2" t="n">
-        <v>11</v>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>CI05029</t>
+        </is>
       </c>
       <c r="D13" s="2" t="n">
         <v>5.36395</v>
@@ -729,8 +753,10 @@
           <t>4G_MarcoryResidentielLagune</t>
         </is>
       </c>
-      <c r="C14" s="2" t="n">
-        <v>12</v>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>CI05050</t>
+        </is>
       </c>
       <c r="D14" s="2" t="n">
         <v>5.31317</v>
@@ -750,8 +776,10 @@
           <t>4G_Niakara2</t>
         </is>
       </c>
-      <c r="C15" s="2" t="n">
-        <v>13</v>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>CI05059</t>
+        </is>
       </c>
       <c r="D15" s="2" t="n">
         <v>8.66005</v>
@@ -771,8 +799,10 @@
           <t>4G_PortBouetJeanFolly2</t>
         </is>
       </c>
-      <c r="C16" s="2" t="n">
-        <v>14</v>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>CI04985</t>
+        </is>
       </c>
       <c r="D16" s="2" t="n">
         <v>5.24233</v>
@@ -792,8 +822,10 @@
           <t>4G_YopougonAnaneraieStationPETROCI</t>
         </is>
       </c>
-      <c r="C17" s="2" t="n">
-        <v>15</v>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>CI04978</t>
+        </is>
       </c>
       <c r="D17" s="2" t="n">
         <v>5.34659</v>
@@ -813,8 +845,10 @@
           <t>4G_YopougonAssomption</t>
         </is>
       </c>
-      <c r="C18" s="2" t="n">
-        <v>16</v>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>CI05044</t>
+        </is>
       </c>
       <c r="D18" s="2" t="n">
         <v>5.33839</v>
@@ -834,8 +868,10 @@
           <t>4G_YopougonEgliseStAndre</t>
         </is>
       </c>
-      <c r="C19" s="2" t="n">
-        <v>17</v>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>CI04974</t>
+        </is>
       </c>
       <c r="D19" s="2" t="n">
         <v>5.34289</v>
@@ -855,8 +891,10 @@
           <t>4G_YopougonNgoh</t>
         </is>
       </c>
-      <c r="C20" s="2" t="n">
-        <v>18</v>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>CI05043</t>
+        </is>
       </c>
       <c r="D20" s="2" t="n">
         <v>5.31949</v>
@@ -876,8 +914,10 @@
           <t>4G_PortBouetSirene2</t>
         </is>
       </c>
-      <c r="C21" s="2" t="n">
-        <v>19</v>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>CI04984</t>
+        </is>
       </c>
       <c r="D21" s="2" t="n">
         <v>5.2518</v>
@@ -897,8 +937,10 @@
           <t>4G_BingerPalaisJustice</t>
         </is>
       </c>
-      <c r="C22" s="2" t="n">
-        <v>20</v>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>CI04433</t>
+        </is>
       </c>
       <c r="D22" s="2" t="n">
         <v>5.34854</v>
@@ -918,8 +960,10 @@
           <t>4G_TreichvilleBelleVille</t>
         </is>
       </c>
-      <c r="C23" s="2" t="n">
-        <v>21</v>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>CI04594</t>
+        </is>
       </c>
       <c r="D23" s="2" t="n">
         <v>5.303145</v>
@@ -939,8 +983,10 @@
           <t>4G_SanPedroCathedrale2</t>
         </is>
       </c>
-      <c r="C24" s="2" t="n">
-        <v>22</v>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>CI04469</t>
+        </is>
       </c>
       <c r="D24" s="2" t="n">
         <v>4.779445</v>
@@ -960,8 +1006,10 @@
           <t>4G_SanpedroBardoNew</t>
         </is>
       </c>
-      <c r="C25" s="2" t="n">
-        <v>23</v>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>CI04398</t>
+        </is>
       </c>
       <c r="D25" s="2" t="n">
         <v>4.783559</v>
@@ -981,8 +1029,10 @@
           <t>4G_ManCNPS</t>
         </is>
       </c>
-      <c r="C26" s="2" t="n">
-        <v>24</v>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>CI04458</t>
+        </is>
       </c>
       <c r="D26" s="2" t="n">
         <v>7.373514</v>
@@ -1002,8 +1052,10 @@
           <t>4G_AllokoiUsineDangoteCement</t>
         </is>
       </c>
-      <c r="C27" s="2" t="n">
-        <v>25</v>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>CI05079</t>
+        </is>
       </c>
       <c r="D27" s="2" t="n">
         <v>5.444202</v>
@@ -1023,8 +1075,10 @@
           <t>4G_PAILLOTE</t>
         </is>
       </c>
-      <c r="C28" s="2" t="n">
-        <v>26</v>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>CI02388</t>
+        </is>
       </c>
       <c r="D28" s="2" t="n">
         <v>5.93537</v>
@@ -1044,8 +1098,10 @@
           <t>4G_Akoviebo</t>
         </is>
       </c>
-      <c r="C29" s="2" t="n">
-        <v>27</v>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>CI02240</t>
+        </is>
       </c>
       <c r="D29" s="2" t="n">
         <v>6.946091</v>
@@ -1065,8 +1121,10 @@
           <t>4G_Dotenzia</t>
         </is>
       </c>
-      <c r="C30" s="2" t="n">
-        <v>28</v>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>CI00760</t>
+        </is>
       </c>
       <c r="D30" s="2" t="n">
         <v>6.98508333</v>
@@ -1086,8 +1144,10 @@
           <t>4G_Nanwokaha</t>
         </is>
       </c>
-      <c r="C31" s="2" t="n">
-        <v>29</v>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>CI02216</t>
+        </is>
       </c>
       <c r="D31" s="2" t="n">
         <v>8.89127</v>
@@ -1107,8 +1167,10 @@
           <t>4G_Mberrie</t>
         </is>
       </c>
-      <c r="C32" s="2" t="n">
-        <v>30</v>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>CI03142</t>
+        </is>
       </c>
       <c r="D32" s="2" t="n">
         <v>6.955272</v>
@@ -1128,8 +1190,10 @@
           <t>4G_Abigui</t>
         </is>
       </c>
-      <c r="C33" s="2" t="n">
-        <v>31</v>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>CI03129</t>
+        </is>
       </c>
       <c r="D33" s="2" t="n">
         <v>6.70245</v>
@@ -1149,8 +1213,10 @@
           <t>4G_ZIPSiteLoboAkoudzin</t>
         </is>
       </c>
-      <c r="C34" s="2" t="n">
-        <v>32</v>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>CI02375</t>
+        </is>
       </c>
       <c r="D34" s="2" t="n">
         <v>5.851509</v>
@@ -1170,8 +1236,10 @@
           <t>4G_AllokoiZIParadisCosmetique</t>
         </is>
       </c>
-      <c r="C35" s="2" t="n">
-        <v>33</v>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>CI04447</t>
+        </is>
       </c>
       <c r="D35" s="2" t="n">
         <v>5.450121</v>
@@ -1191,8 +1259,10 @@
           <t>4G_ManPouponnière</t>
         </is>
       </c>
-      <c r="C36" s="2" t="n">
-        <v>34</v>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>CI04484</t>
+        </is>
       </c>
       <c r="D36" s="2" t="n">
         <v>7.419751</v>
@@ -1212,8 +1282,10 @@
           <t>4G_DaloaOrlyCentre</t>
         </is>
       </c>
-      <c r="C37" s="2" t="n">
-        <v>35</v>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>CI04472</t>
+        </is>
       </c>
       <c r="D37" s="2" t="n">
         <v>6.843372</v>
@@ -1233,8 +1305,10 @@
           <t>4G_CocodyRivieraGolf4</t>
         </is>
       </c>
-      <c r="C38" s="2" t="n">
-        <v>36</v>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>CI04451</t>
+        </is>
       </c>
       <c r="D38" s="2" t="n">
         <v>5.336361</v>
@@ -1254,8 +1328,10 @@
           <t>4G_AdjameDallas</t>
         </is>
       </c>
-      <c r="C39" s="2" t="n">
-        <v>37</v>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>CI04443</t>
+        </is>
       </c>
       <c r="D39" s="2" t="n">
         <v>5.339367</v>
@@ -1275,8 +1351,10 @@
           <t>4G_DokuiBad</t>
         </is>
       </c>
-      <c r="C40" s="2" t="n">
-        <v>38</v>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>CI04803</t>
+        </is>
       </c>
       <c r="D40" s="2" t="n">
         <v>5.393027</v>
@@ -1296,8 +1374,10 @@
           <t>4G_Modeste3</t>
         </is>
       </c>
-      <c r="C41" s="2" t="n">
-        <v>39</v>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>CI04479</t>
+        </is>
       </c>
       <c r="D41" s="2" t="n">
         <v>5.218407</v>
